--- a/tests/data_golden/preserve.expected.xlsx
+++ b/tests/data_golden/preserve.expected.xlsx
@@ -93,7 +93,7 @@
     <t>static</t>
   </si>
   <si>
-    <t>Customer: Alice</t>
+    <t xml:space="preserve">Customer: Alice</t>
   </si>
 </sst>
 </file>
